--- a/smartshop/EvidenceBasedAdaptiveUI/reports/Feature_Importance/target_predictor_summary.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/Feature_Importance/target_predictor_summary.xlsx
@@ -492,30 +492,30 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.166754478221572</v>
+        <v>0.154302547196298</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neuroticism, Openness, Conscientiousness</t>
+          <t>Neuroticism, Openness, Extraversion</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.1668, 0.1505, 0.1386</t>
+          <t>0.1543, 0.1529, 0.1404</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>primary_device, Neuroticism, current_mood</t>
+          <t>primary_device, Neuroticism, primary_persona</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0483, 0.0418, 0.0311</t>
+          <t>0.0381, 0.0299, 0.0282</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.04828259122900901</v>
+        <v>0.03809923856570584</v>
       </c>
     </row>
     <row r="3">
@@ -535,30 +535,30 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1750392083298654</v>
+        <v>0.156376594392571</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neuroticism, Extraversion, Agreeableness</t>
+          <t>Neuroticism, Agreeableness, Extraversion</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.1750, 0.1392, 0.1336</t>
+          <t>0.1564, 0.1440, 0.1414</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>current_mood, primary_persona, Extraversion</t>
+          <t>current_mood, Conscientiousness, Neuroticism</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0462, 0.0355, 0.0321</t>
+          <t>0.0276, 0.0261, 0.0249</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.04615599483440821</v>
+        <v>0.02755243525333835</v>
       </c>
     </row>
     <row r="4">
@@ -574,34 +574,34 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1615434309580455</v>
+        <v>0.147515215313564</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>primary_persona, Neuroticism, current_mood</t>
+          <t>Neuroticism, primary_persona, Conscientiousness</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.1615, 0.1456, 0.1414</t>
+          <t>0.1475, 0.1452, 0.1419</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>primary_persona, Agreeableness, Neuroticism</t>
+          <t>Neuroticism, Openness, Extraversion</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0297, 0.0236, 0.0201</t>
+          <t>0.0301, 0.0238, 0.0220</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.0297348840435253</v>
+        <v>0.03011478526552338</v>
       </c>
     </row>
     <row r="5">
@@ -617,34 +617,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.1469942778243226</v>
+        <v>0.1456517975149239</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>current_mood, Openness, Conscientiousness</t>
+          <t>Agreeableness, Neuroticism, current_mood</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.1470, 0.1450, 0.1422</t>
+          <t>0.1457, 0.1423, 0.1419</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Openness, Neuroticism, current_mood</t>
+          <t>Neuroticism, primary_persona, Agreeableness</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0274, 0.0197, 0.0191</t>
+          <t>0.0205, 0.0205, 0.0198</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.02736537406851321</v>
+        <v>0.02052478693461994</v>
       </c>
     </row>
     <row r="6">
@@ -664,30 +664,30 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.1539018391354902</v>
+        <v>0.1644723132958532</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Neuroticism, Conscientiousness, primary_persona</t>
+          <t>Neuroticism, primary_persona, Conscientiousness</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.1539, 0.1407, 0.1361</t>
+          <t>0.1645, 0.1426, 0.1349</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>current_mood, Neuroticism, Extraversion</t>
+          <t>Agreeableness, Neuroticism, Extraversion</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0483, 0.0318, 0.0272</t>
+          <t>0.0356, 0.0295, 0.0256</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.04828990137877086</v>
+        <v>0.03562855577852648</v>
       </c>
     </row>
     <row r="7">
@@ -703,34 +703,34 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.1507784783512724</v>
+        <v>0.1582355616342049</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>Conscientiousness, Neuroticism, Openness</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.1582, 0.1499, 0.1376</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>current_mood, Neuroticism, Extraversion</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0.1508, 0.1506, 0.1440</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Openness, Neuroticism, Conscientiousness</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0339, 0.0300, 0.0261</t>
+          <t>0.0382, 0.0323, 0.0305</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.03388854266615276</v>
+        <v>0.0382447927828469</v>
       </c>
     </row>
     <row r="8">
@@ -750,30 +750,30 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.1666568725148211</v>
+        <v>0.151966046643596</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Neuroticism, Conscientiousness, Extraversion</t>
+          <t>Neuroticism, Openness, Conscientiousness</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.1667, 0.1406, 0.1381</t>
+          <t>0.1520, 0.1427, 0.1397</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Agreeableness, Openness, current_mood</t>
+          <t>Agreeableness, Extraversion, Neuroticism</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0250, 0.0244, 0.0219</t>
+          <t>0.0229, 0.0229, 0.0220</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.02504461504999842</v>
+        <v>0.02293622100741881</v>
       </c>
     </row>
     <row r="9">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.1608969971318128</v>
+        <v>0.1653523498251288</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.1609, 0.1453, 0.1421</t>
+          <t>0.1654, 0.1465, 0.1443</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>current_mood, Openness, primary_device</t>
+          <t>primary_device, Openness, Neuroticism</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0408, 0.0405, 0.0306</t>
+          <t>0.0344, 0.0311, 0.0282</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.04078750777312464</v>
+        <v>0.03436380317597383</v>
       </c>
     </row>
     <row r="10">
@@ -836,30 +836,30 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1540470577757507</v>
+        <v>0.1559057778329406</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Neuroticism, Agreeableness, Extraversion</t>
+          <t>Neuroticism, Conscientiousness, primary_persona</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.1540, 0.1435, 0.1403</t>
+          <t>0.1559, 0.1455, 0.1407</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neuroticism, primary_persona, current_mood</t>
+          <t>Neuroticism, current_mood, Agreeableness</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0406, 0.0362, 0.0311</t>
+          <t>0.0443, 0.0345, 0.0309</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.04055553676141661</v>
+        <v>0.04434580723534823</v>
       </c>
     </row>
     <row r="11">
@@ -879,30 +879,30 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1605640408199236</v>
+        <v>0.151058511953328</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Neuroticism, Conscientiousness, primary_persona</t>
+          <t>Neuroticism, primary_persona, Conscientiousness</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.1606, 0.1469, 0.1468</t>
+          <t>0.1511, 0.1466, 0.1448</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neuroticism, Extraversion, primary_device</t>
+          <t>Neuroticism, primary_persona, Agreeableness</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.0315, 0.0252, 0.0230</t>
+          <t>0.0376, 0.0305, 0.0258</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.03152006716729635</v>
+        <v>0.03758177776032348</v>
       </c>
     </row>
     <row r="12">
@@ -922,30 +922,30 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.1541881133878216</v>
+        <v>0.1452802570235586</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Neuroticism, primary_persona, Conscientiousness</t>
+          <t>Neuroticism, Openness, Extraversion</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.1542, 0.1436, 0.1400</t>
+          <t>0.1453, 0.1414, 0.1364</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>primary_device, Neuroticism, current_mood</t>
+          <t>current_mood, primary_device, Agreeableness</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.0320, 0.0309, 0.0304</t>
+          <t>0.0356, 0.0340, 0.0320</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.03197838174348877</v>
+        <v>0.03563454222560034</v>
       </c>
     </row>
     <row r="13">
@@ -965,30 +965,30 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.1724525874473294</v>
+        <v>0.1645700749107897</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Neuroticism, Conscientiousness, primary_persona</t>
+          <t>Neuroticism, Conscientiousness, Agreeableness</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.1725, 0.1614, 0.1333</t>
+          <t>0.1646, 0.1485, 0.1443</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Extraversion, current_mood, primary_device</t>
+          <t>primary_persona, Extraversion, current_mood</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.0310, 0.0303, 0.0247</t>
+          <t>0.0313, 0.0292, 0.0288</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.03097613547193547</v>
+        <v>0.03128778135807331</v>
       </c>
     </row>
     <row r="14">
@@ -1008,30 +1008,30 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.1586690174594589</v>
+        <v>0.149965430738608</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>primary_persona, Extraversion, Conscientiousness</t>
+          <t>primary_persona, Neuroticism, Agreeableness</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.1587, 0.1409, 0.1403</t>
+          <t>0.1500, 0.1407, 0.1368</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Agreeableness, primary_persona, Openness</t>
+          <t>primary_persona, current_mood, Conscientiousness</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0233, 0.0205, 0.0196</t>
+          <t>0.0200, 0.0182, 0.0181</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.02330734089617804</v>
+        <v>0.01998120909333736</v>
       </c>
     </row>
     <row r="15">
@@ -1047,34 +1047,34 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.1540095354726442</v>
+        <v>0.1488443327461026</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>primary_persona, Neuroticism, Agreeableness</t>
+          <t>Neuroticism, Agreeableness, Openness</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.1540, 0.1496, 0.1384</t>
+          <t>0.1488, 0.1469, 0.1428</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>primary_persona, Openness, Neuroticism</t>
+          <t>Conscientiousness, primary_device, Agreeableness</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.0410, 0.0343, 0.0338</t>
+          <t>0.0349, 0.0343, 0.0324</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.0409993870133311</v>
+        <v>0.03490515958752668</v>
       </c>
     </row>
     <row r="16">
@@ -1090,34 +1090,34 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.1489653337645632</v>
+        <v>0.1512893293587264</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Agreeableness, Conscientiousness, Neuroticism</t>
+          <t>Conscientiousness, Neuroticism, Agreeableness</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.1490, 0.1471, 0.1392</t>
+          <t>0.1513, 0.1451, 0.1404</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Openness, Agreeableness, current_mood</t>
+          <t>Neuroticism, Conscientiousness, primary_persona</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.0256, 0.0248, 0.0223</t>
+          <t>0.0281, 0.0276, 0.0244</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.02560316819262314</v>
+        <v>0.02811945678219669</v>
       </c>
     </row>
     <row r="17">
@@ -1137,30 +1137,30 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.1516035561058999</v>
+        <v>0.1586560731382151</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Neuroticism, Extraversion, primary_persona</t>
+          <t>Neuroticism, Openness, primary_persona</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.1516, 0.1495, 0.1406</t>
+          <t>0.1587, 0.1431, 0.1402</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neuroticism, primary_device, current_mood</t>
+          <t>primary_device, Neuroticism, current_mood</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.0366, 0.0360, 0.0338</t>
+          <t>0.0334, 0.0326, 0.0306</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.03661318172966233</v>
+        <v>0.03341680169935241</v>
       </c>
     </row>
     <row r="18">
@@ -1176,34 +1176,34 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.1475917128710594</v>
+        <v>0.1498991259733833</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Neuroticism, Agreeableness, primary_persona</t>
+          <t>Conscientiousness, Neuroticism, Agreeableness</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.1476, 0.1420, 0.1413</t>
+          <t>0.1499, 0.1487, 0.1460</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neuroticism, Openness, Agreeableness</t>
+          <t>Conscientiousness, Neuroticism, primary_persona</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.0350, 0.0318, 0.0282</t>
+          <t>0.0396, 0.0389, 0.0335</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.03501225697927684</v>
+        <v>0.03963501720258204</v>
       </c>
     </row>
     <row r="19">
@@ -1223,30 +1223,30 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.1734640320746739</v>
+        <v>0.1594405556880039</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Neuroticism, Openness, Conscientiousness</t>
+          <t>Neuroticism, Openness, Agreeableness</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.1735, 0.1500, 0.1410</t>
+          <t>0.1594, 0.1509, 0.1396</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>primary_device, Openness, Agreeableness</t>
+          <t>Conscientiousness, primary_device, Extraversion</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.0450, 0.0338, 0.0299</t>
+          <t>0.0376, 0.0308, 0.0273</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.04497102499333076</v>
+        <v>0.03764689293797543</v>
       </c>
     </row>
     <row r="20">
@@ -1266,30 +1266,30 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.1469126294681928</v>
+        <v>0.1538892887108169</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neuroticism, Openness, primary_persona</t>
+          <t>Neuroticism, Openness, Agreeableness</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.1469, 0.1438, 0.1381</t>
+          <t>0.1539, 0.1477, 0.1402</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Agreeableness, primary_device, Neuroticism</t>
+          <t>current_mood, Neuroticism, primary_device</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.0352, 0.0336, 0.0330</t>
+          <t>0.0358, 0.0293, 0.0250</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.03521455900801927</v>
+        <v>0.03582976720680696</v>
       </c>
     </row>
     <row r="21">
@@ -1309,30 +1309,30 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.1688294095120784</v>
+        <v>0.1554617319292695</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Neuroticism, Agreeableness, Conscientiousness</t>
+          <t>Neuroticism, Agreeableness, Extraversion</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.1688, 0.1579, 0.1316</t>
+          <t>0.1555, 0.1495, 0.1433</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Extraversion, primary_persona, Agreeableness</t>
+          <t>current_mood, Agreeableness, Conscientiousness</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.0495, 0.0354, 0.0254</t>
+          <t>0.0367, 0.0297, 0.0262</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.04953568965636855</v>
+        <v>0.03669277804637983</v>
       </c>
     </row>
     <row r="22">
@@ -1352,30 +1352,30 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.1593344978022734</v>
+        <v>0.1621265897738878</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Neuroticism, Conscientiousness, Extraversion</t>
+          <t>Neuroticism, Conscientiousness, Agreeableness</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.1593, 0.1521, 0.1386</t>
+          <t>0.1621, 0.1396, 0.1376</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Agreeableness, primary_persona, current_mood</t>
+          <t>primary_persona, Openness, Conscientiousness</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.0364, 0.0330, 0.0246</t>
+          <t>0.0311, 0.0309, 0.0302</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.0363836631085862</v>
+        <v>0.03110389560142154</v>
       </c>
     </row>
     <row r="23">
@@ -1395,30 +1395,30 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.1601909869000728</v>
+        <v>0.156096636722261</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Neuroticism, Conscientiousness, primary_persona</t>
+          <t>Neuroticism, Openness, Conscientiousness</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.1602, 0.1421, 0.1375</t>
+          <t>0.1561, 0.1416, 0.1347</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neuroticism, Openness, Agreeableness</t>
+          <t>Neuroticism, primary_persona, Agreeableness</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.0282, 0.0246, 0.0242</t>
+          <t>0.0289, 0.0260, 0.0259</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.02815128451829332</v>
+        <v>0.02885014099936915</v>
       </c>
     </row>
     <row r="24">
@@ -1438,30 +1438,30 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.1487447892060389</v>
+        <v>0.150012559438695</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Neuroticism, Conscientiousness, Agreeableness</t>
+          <t>Neuroticism, primary_persona, Extraversion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.1487, 0.1481, 0.1383</t>
+          <t>0.1500, 0.1493, 0.1394</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Conscientiousness, Openness, primary_device</t>
+          <t>primary_persona, Neuroticism, Conscientiousness</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.0401, 0.0351, 0.0288</t>
+          <t>0.0362, 0.0331, 0.0260</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.04011943385433388</v>
+        <v>0.03622596838859769</v>
       </c>
     </row>
     <row r="25">
@@ -1481,30 +1481,30 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.1557646206679608</v>
+        <v>0.1515395151341888</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Agreeableness, Neuroticism, primary_persona</t>
+          <t>Agreeableness, current_mood, Extraversion</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.1558, 0.1554, 0.1418</t>
+          <t>0.1515, 0.1473, 0.1390</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Extraversion, current_mood, Openness</t>
+          <t>Neuroticism, primary_persona, current_mood</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.0467, 0.0425, 0.0277</t>
+          <t>0.0498, 0.0293, 0.0269</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.04672734454016356</v>
+        <v>0.04976062206013869</v>
       </c>
     </row>
     <row r="26">
@@ -1524,30 +1524,30 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.1670212648937824</v>
+        <v>0.162995294493098</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Neuroticism, current_mood, Openness</t>
+          <t>Neuroticism, current_mood, Extraversion</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.1670, 0.1461, 0.1320</t>
+          <t>0.1630, 0.1601, 0.1382</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Openness, primary_persona, Extraversion</t>
+          <t>Agreeableness, current_mood, Extraversion</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.0360, 0.0356, 0.0297</t>
+          <t>0.0421, 0.0400, 0.0383</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.03601509161981057</v>
+        <v>0.04210615145277036</v>
       </c>
     </row>
     <row r="27">
@@ -1563,34 +1563,34 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.160271276894365</v>
+        <v>0.1578908535418077</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Agreeableness, Neuroticism, Openness</t>
+          <t>Neuroticism, Agreeableness, Openness</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.1603, 0.1588, 0.1342</t>
+          <t>0.1579, 0.1534, 0.1426</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Extraversion, current_mood, primary_device</t>
+          <t>primary_persona, Extraversion, primary_device</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.0285, 0.0277, 0.0235</t>
+          <t>0.0349, 0.0310, 0.0262</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.02853896711768724</v>
+        <v>0.03492245695292501</v>
       </c>
     </row>
     <row r="28">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.1573615280668692</v>
+        <v>0.1590698535013453</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Neuroticism, Conscientiousness, Agreeableness</t>
+          <t>Conscientiousness, Neuroticism, Agreeableness</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.1574, 0.1515, 0.1353</t>
+          <t>0.1591, 0.1504, 0.1461</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neuroticism, current_mood, Extraversion</t>
+          <t>current_mood, primary_device, Extraversion</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.0367, 0.0305, 0.0299</t>
+          <t>0.0360, 0.0351, 0.0340</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.03666279100423075</v>
+        <v>0.03597010550148029</v>
       </c>
     </row>
     <row r="29">
@@ -1653,30 +1653,30 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.1546248308414427</v>
+        <v>0.1654255045657358</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Neuroticism, Openness, Conscientiousness</t>
+          <t>Neuroticism, Agreeableness, Conscientiousness</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.1546, 0.1465, 0.1433</t>
+          <t>0.1654, 0.1411, 0.1384</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>primary_persona, Extraversion, Conscientiousness</t>
+          <t>current_mood, primary_persona, Extraversion</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.0355, 0.0309, 0.0277</t>
+          <t>0.0334, 0.0328, 0.0316</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.03547752808433706</v>
+        <v>0.03338474742164872</v>
       </c>
     </row>
     <row r="30">
@@ -1692,34 +1692,34 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.1632939342843895</v>
+        <v>0.175575704624629</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Openness, Neuroticism, Conscientiousness</t>
+          <t>Neuroticism, Conscientiousness, Openness</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.1633, 0.1595, 0.1367</t>
+          <t>0.1756, 0.1385, 0.1377</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>primary_device, Openness, Extraversion</t>
+          <t>Agreeableness, primary_device, primary_persona</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.0414, 0.0256, 0.0215</t>
+          <t>0.0389, 0.0389, 0.0291</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.04135348618317817</v>
+        <v>0.03890354667296107</v>
       </c>
     </row>
     <row r="31">
@@ -1739,30 +1739,30 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.1733818332768428</v>
+        <v>0.1644936083843054</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Neuroticism, primary_persona, Conscientiousness</t>
+          <t>Neuroticism, Conscientiousness, Openness</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.1734, 0.1520, 0.1456</t>
+          <t>0.1645, 0.1597, 0.1475</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neuroticism, Agreeableness, current_mood</t>
+          <t>Neuroticism, primary_device, Extraversion</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.0295, 0.0289, 0.0263</t>
+          <t>0.0308, 0.0226, 0.0203</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.02946579695653979</v>
+        <v>0.03077182763434903</v>
       </c>
     </row>
     <row r="32">
@@ -1782,30 +1782,30 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.1753688720402702</v>
+        <v>0.1634285959043757</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Conscientiousness, primary_persona, Neuroticism</t>
+          <t>Conscientiousness, Neuroticism, primary_persona</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.1754, 0.1430, 0.1415</t>
+          <t>0.1634, 0.1522, 0.1402</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Agreeableness, Conscientiousness, current_mood</t>
+          <t>current_mood, primary_device, Conscientiousness</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.0237, 0.0220, 0.0213</t>
+          <t>0.0218, 0.0197, 0.0188</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.02371277463343708</v>
+        <v>0.02183006711368665</v>
       </c>
     </row>
     <row r="33">
@@ -1821,34 +1821,34 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1543263702222125</v>
+        <v>0.171996073879084</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Openness, Neuroticism, Conscientiousness</t>
+          <t>Neuroticism, Openness, Conscientiousness</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.1543, 0.1515, 0.1421</t>
+          <t>0.1720, 0.1430, 0.1391</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>primary_device, primary_persona, Extraversion</t>
+          <t>primary_device, primary_persona, current_mood</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.0449, 0.0297, 0.0283</t>
+          <t>0.0315, 0.0271, 0.0252</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.04493073745636021</v>
+        <v>0.03150951223570677</v>
       </c>
     </row>
     <row r="34">
@@ -1868,30 +1868,30 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.1682407298905595</v>
+        <v>0.1651365657207518</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Conscientiousness, Extraversion, Neuroticism</t>
+          <t>Conscientiousness, Neuroticism, Extraversion</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.1682, 0.1446, 0.1396</t>
+          <t>0.1651, 0.1572, 0.1408</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>current_mood, Agreeableness, primary_device</t>
+          <t>primary_persona, Conscientiousness, primary_device</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.0511, 0.0335, 0.0281</t>
+          <t>0.0467, 0.0343, 0.0325</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.05113542234606927</v>
+        <v>0.04671541749956636</v>
       </c>
     </row>
     <row r="35">
@@ -1907,34 +1907,34 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.1729821141017556</v>
+        <v>0.1641360042788341</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Openness, Neuroticism, Extraversion</t>
+          <t>current_mood, Neuroticism, Extraversion</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.1730, 0.1482, 0.1445</t>
+          <t>0.1641, 0.1463, 0.1323</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>primary_device, primary_persona, Openness</t>
+          <t>Neuroticism, primary_device, primary_persona</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.0533, 0.0339, 0.0300</t>
+          <t>0.0448, 0.0440, 0.0419</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.0532851628336115</v>
+        <v>0.04482279937278525</v>
       </c>
     </row>
     <row r="36">
@@ -1954,30 +1954,30 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.1552991183420361</v>
+        <v>0.1612596853077023</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Neuroticism, Conscientiousness, current_mood</t>
+          <t>Neuroticism, Agreeableness, Conscientiousness</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.1553, 0.1421, 0.1410</t>
+          <t>0.1613, 0.1402, 0.1360</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Conscientiousness, primary_persona, Openness</t>
+          <t>Extraversion, Neuroticism, primary_persona</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.0308, 0.0266, 0.0266</t>
+          <t>0.0259, 0.0205, 0.0189</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.0307658410250342</v>
+        <v>0.0258639928405956</v>
       </c>
     </row>
     <row r="37">
@@ -1997,30 +1997,30 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.1633089165970898</v>
+        <v>0.1785808417698981</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Neuroticism, Conscientiousness, current_mood</t>
+          <t>Neuroticism, Conscientiousness, primary_persona</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.1633, 0.1461, 0.1364</t>
+          <t>0.1786, 0.1490, 0.1378</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>primary_persona, Openness, Neuroticism</t>
+          <t>Neuroticism, Openness, current_mood</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.0325, 0.0315, 0.0309</t>
+          <t>0.0499, 0.0359, 0.0335</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.03249707758068944</v>
+        <v>0.04985584668767024</v>
       </c>
     </row>
     <row r="38">
@@ -2036,34 +2036,34 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.1480683053593875</v>
+        <v>0.1424409720450504</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Openness, Extraversion, current_mood</t>
+          <t>current_mood, Openness, Conscientiousness</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.1481, 0.1460, 0.1444</t>
+          <t>0.1424, 0.1419, 0.1392</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>primary_device, Extraversion, primary_persona</t>
+          <t>Openness, primary_device, current_mood</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.0513, 0.0393, 0.0330</t>
+          <t>0.0316, 0.0307, 0.0282</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.05132729692284529</v>
+        <v>0.03155657743988236</v>
       </c>
     </row>
     <row r="39">
@@ -2083,30 +2083,30 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.1589016105693498</v>
+        <v>0.1535727242355789</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Neuroticism, Conscientiousness, primary_persona</t>
+          <t>Neuroticism, Conscientiousness, Openness</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.1589, 0.1409, 0.1383</t>
+          <t>0.1536, 0.1508, 0.1474</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Extraversion, Neuroticism, primary_device</t>
+          <t>Extraversion, Neuroticism, primary_persona</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.0493, 0.0373, 0.0335</t>
+          <t>0.0414, 0.0351, 0.0316</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.04928554520545893</v>
+        <v>0.04136453319739312</v>
       </c>
     </row>
     <row r="40">
@@ -2126,30 +2126,30 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.1642596312543621</v>
+        <v>0.1650522394304711</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Neuroticism, Extraversion, Conscientiousness</t>
+          <t>Neuroticism, Extraversion, Agreeableness</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.1643, 0.1420, 0.1419</t>
+          <t>0.1651, 0.1455, 0.1412</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>primary_persona, Agreeableness, current_mood</t>
+          <t>Conscientiousness, primary_persona, Neuroticism</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.0468, 0.0459, 0.0313</t>
+          <t>0.0418, 0.0378, 0.0286</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.0467966667694255</v>
+        <v>0.04180842022227619</v>
       </c>
     </row>
     <row r="41">
@@ -2165,34 +2165,34 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.1516358121404803</v>
+        <v>0.1608578546875862</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Neuroticism, Agreeableness, current_mood</t>
+          <t>Agreeableness, primary_persona, Neuroticism</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.1516, 0.1489, 0.1452</t>
+          <t>0.1609, 0.1463, 0.1453</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Agreeableness, Neuroticism, Extraversion</t>
+          <t>primary_device, Agreeableness, Conscientiousness</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.0781, 0.0426, 0.0412</t>
+          <t>0.0456, 0.0407, 0.0405</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.07812896262476739</v>
+        <v>0.04557040654893607</v>
       </c>
     </row>
     <row r="42">
@@ -2212,30 +2212,30 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.1547788099463741</v>
+        <v>0.170288284218379</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Neuroticism, Agreeableness, Openness</t>
+          <t>Neuroticism, Openness, Agreeableness</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.1548, 0.1422, 0.1414</t>
+          <t>0.1703, 0.1441, 0.1414</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Agreeableness, Neuroticism, primary_device</t>
+          <t>Neuroticism, primary_device, primary_persona</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.0434, 0.0334, 0.0287</t>
+          <t>0.0379, 0.0331, 0.0251</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.04343956370071127</v>
+        <v>0.03794284672896697</v>
       </c>
     </row>
   </sheetData>
